--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484716_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484716_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3511</v>
+        <v>0.6499</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.1695</v>
+        <v>-2.1035</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5206</v>
+        <v>2.7534</v>
       </c>
       <c r="G2" t="n">
         <v>-2.2466</v>
@@ -610,13 +610,13 @@
         <v>4.1514</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2502</v>
+        <v>1.549</v>
       </c>
       <c r="T2" t="n">
-        <v>1.744</v>
+        <v>0.8099</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5062</v>
+        <v>0.739</v>
       </c>
       <c r="V2" t="n">
         <v>0.2152</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0264</v>
+        <v>0.1117</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6872</v>
+        <v>-0.6284</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7136</v>
+        <v>0.7401</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4985</v>
@@ -688,13 +688,13 @@
         <v>0.5661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0412</v>
+        <v>0.0441</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0588</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>J. CONNELLY IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.2115</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8259</v>
+        <v>2.4905</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2901</v>
+        <v>-2.702</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9908</v>
+        <v>3.7473</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1207</v>
+        <v>-0.1119</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1299</v>
+        <v>3.8592</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2991</v>
+        <v>7.4531</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2991</v>
+        <v>2.4252</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5.0279</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3083</v>
+        <v>-3.7058</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1784</v>
+        <v>-2.5371</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1299</v>
+        <v>-1.1687</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-2.6418</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-5.8497</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.2079</v>
       </c>
       <c r="S4" t="n">
-        <v>0.455</v>
+        <v>-0.8716</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4732</v>
+        <v>-0.3391</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0182</v>
+        <v>-0.5325</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.4453</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.6715</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CONNELLY IV</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.6513</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0218</v>
+        <v>-1.0208</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.6755</v>
+        <v>0.3695</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7473</v>
+        <v>-0.9908</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1119</v>
+        <v>-1.1207</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8592</v>
+        <v>0.1299</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4531</v>
+        <v>-1.2991</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4252</v>
+        <v>-1.2991</v>
       </c>
       <c r="L5" t="n">
-        <v>5.0279</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7058</v>
+        <v>0.3083</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.5371</v>
+        <v>0.1784</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1687</v>
+        <v>0.1299</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.6418</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.8497</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2079</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3139</v>
+        <v>0.3395</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8078</v>
+        <v>0.2783</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5061</v>
+        <v>0.0611</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4453</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2262</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3726</v>
+        <v>-1.6645</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2931</v>
+        <v>-0.5321</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0795</v>
+        <v>-1.1324</v>
       </c>
       <c r="G7" t="n">
         <v>-3.8059</v>
@@ -1000,13 +1000,13 @@
         <v>4.5288</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8388</v>
+        <v>-1.1307</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.8101</v>
+        <v>-1.0491</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0287</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1245</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4333</v>
+        <v>-1.8525</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2649</v>
+        <v>-2.8163</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8316</v>
+        <v>0.9639</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8794</v>
@@ -1078,13 +1078,13 @@
         <v>2.2644</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6296</v>
+        <v>-0.0488</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7519</v>
+        <v>-0.3034</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1223</v>
+        <v>0.2546</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9884</v>
+        <v>-4.1728</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.1026</v>
+        <v>-5.4722</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1142</v>
+        <v>1.2993</v>
       </c>
       <c r="G9" t="n">
         <v>-5.3326</v>
@@ -1156,13 +1156,13 @@
         <v>2.6418</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2686</v>
+        <v>0.0842</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6089</v>
+        <v>0.2393</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3403</v>
+        <v>-0.1551</v>
       </c>
       <c r="V9" t="n">
         <v>0.3208</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3414</v>
+        <v>-4.1768</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0621</v>
+        <v>-4.0033</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2792</v>
+        <v>-0.1734</v>
       </c>
       <c r="G10" t="n">
         <v>-6.6788</v>
@@ -1234,13 +1234,13 @@
         <v>3.2079</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7648</v>
+        <v>-0.6002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3839</v>
+        <v>-0.3252</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3809</v>
+        <v>-0.2751</v>
       </c>
       <c r="V10" t="n">
         <v>0.8378</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1067</v>
+        <v>-4.8245</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.4854</v>
+        <v>-7.3091</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3787</v>
+        <v>2.4845</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7846</v>
@@ -1312,13 +1312,13 @@
         <v>3.3966</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2916</v>
+        <v>-0.0094</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1582</v>
+        <v>0.0181</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1334</v>
+        <v>-0.0276</v>
       </c>
       <c r="V11" t="n">
         <v>0.4791</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9904</v>
+        <v>-5.0766</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1866</v>
+        <v>-3.4844</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8038</v>
+        <v>-1.5922</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9877</v>
@@ -1390,13 +1390,13 @@
         <v>2.2644</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.248</v>
+        <v>-0.3342</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9871</v>
+        <v>-0.2849</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.261</v>
+        <v>-0.0493</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9434</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.2663</v>
+        <v>-23.0904</v>
       </c>
       <c r="E13" t="n">
-        <v>-26.1979</v>
+        <v>-25.022</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9317</v>
+        <v>1.9316</v>
       </c>
       <c r="G13" t="n">
         <v>-25.618</v>
@@ -1468,13 +1468,13 @@
         <v>26.418</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.4604</v>
+        <v>-1.2844</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3081</v>
+        <v>-1.1325</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1523999999999999</v>
+        <v>-0.1523</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9055000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2529</v>
+        <v>6.4455</v>
       </c>
       <c r="E14" t="n">
-        <v>2.227</v>
+        <v>2.4219</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0259</v>
+        <v>4.0236</v>
       </c>
       <c r="G14" t="n">
         <v>5.2829</v>
@@ -1546,13 +1546,13 @@
         <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5926</v>
+        <v>0.7851</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2199</v>
+        <v>-0.025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8125</v>
+        <v>0.8102</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.5131</v>
+        <v>6.3321</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6547</v>
+        <v>2.947</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8583</v>
+        <v>3.3851</v>
       </c>
       <c r="G15" t="n">
         <v>3.7312</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3503</v>
+        <v>-0.5313</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7642</v>
+        <v>-0.4719</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5861</v>
+        <v>-0.0593</v>
       </c>
       <c r="V15" t="n">
         <v>1.2452</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8971</v>
+        <v>4.7301</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9517</v>
+        <v>0.9685</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9454</v>
+        <v>3.7616</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6172</v>
+        <v>3.0559</v>
       </c>
       <c r="H16" t="n">
-        <v>2.394</v>
+        <v>0.7802</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2232</v>
+        <v>2.2757</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7299</v>
+        <v>1.6118</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6802</v>
+        <v>0.8303</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0496</v>
+        <v>0.7815</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8873</v>
+        <v>1.4442</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7137</v>
+        <v>-0.0501</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1736</v>
+        <v>1.4943</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5661</v>
+        <v>1.1322</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0757</v>
+        <v>-1.1322</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5096</v>
+        <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5443</v>
+        <v>-0.0617</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3731</v>
+        <v>-0.1147</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1711</v>
+        <v>0.053</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3018</v>
+        <v>0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>0.9244</v>
+        <v>0.6036</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6002</v>
+        <v>3.4094</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9685</v>
+        <v>1.0748</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6317</v>
+        <v>2.3346</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0559</v>
+        <v>2.6172</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7802</v>
+        <v>2.394</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2757</v>
+        <v>0.2232</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6118</v>
+        <v>1.7299</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8303</v>
+        <v>1.6802</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7815</v>
+        <v>0.0496</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4442</v>
+        <v>0.8873</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0501</v>
+        <v>0.7137</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4943</v>
+        <v>0.1736</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1322</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2644</v>
+        <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1916</v>
+        <v>1.0565</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1147</v>
+        <v>0.4962</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0769</v>
+        <v>0.5603</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6036</v>
+        <v>0.3018</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036</v>
+        <v>0.9244</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9502</v>
+        <v>2.8444</v>
       </c>
       <c r="E18" t="n">
         <v>0.2345</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7157</v>
+        <v>2.6099</v>
       </c>
       <c r="G18" t="n">
         <v>2.1843</v>
@@ -1858,13 +1858,13 @@
         <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9165</v>
+        <v>0.8107</v>
       </c>
       <c r="T18" t="n">
         <v>0.0152</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9013</v>
+        <v>0.7955</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9054</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.109</v>
+        <v>2.1242</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1973</v>
+        <v>-2.4179</v>
       </c>
       <c r="F19" t="n">
-        <v>4.3064</v>
+        <v>4.5421</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2772</v>
@@ -1936,13 +1936,13 @@
         <v>3.5853</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7459</v>
+        <v>0.2693</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1634</v>
+        <v>-0.3839</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4175</v>
+        <v>0.6532</v>
       </c>
       <c r="V19" t="n">
         <v>0.6226</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SUCH LOPEZ</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9589</v>
+        <v>0.9509</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5724</v>
+        <v>0.9509</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5313</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8501</v>
+        <v>0.9509</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4408</v>
+        <v>0.9509</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4093</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0765</v>
+        <v>0.9509</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0354</v>
+        <v>0.9509</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7736</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4054</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3682</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0523</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1857</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,31 +2047,31 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9509</v>
+        <v>0.9339</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9509</v>
+        <v>0.9339</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9509</v>
+        <v>0.9339</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9509</v>
+        <v>0.317</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.617</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9509</v>
+        <v>0.9339</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9509</v>
+        <v>0.317</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.617</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>A. SUCH LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9339</v>
+        <v>0.912</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9339</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.5819</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9339</v>
+        <v>1.8501</v>
       </c>
       <c r="H22" t="n">
-        <v>0.317</v>
+        <v>1.4408</v>
       </c>
       <c r="I22" t="n">
-        <v>0.617</v>
+        <v>0.4093</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9339</v>
+        <v>1.0765</v>
       </c>
       <c r="K22" t="n">
-        <v>0.317</v>
+        <v>1.0354</v>
       </c>
       <c r="L22" t="n">
-        <v>0.617</v>
+        <v>0.0411</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.7736</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.4054</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.3682</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>0.1406</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>-0.1352</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4223</v>
+        <v>-0.5595</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5928</v>
+        <v>-1.1774</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1705</v>
+        <v>0.6179</v>
       </c>
       <c r="G23" t="n">
         <v>0.7595</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5919</v>
+        <v>0.4547</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.1266</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1193</v>
+        <v>0.3281</v>
       </c>
       <c r="V23" t="n">
         <v>-1.585</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1772</v>
+        <v>-1.0041</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0848</v>
+        <v>-3.2796</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9075</v>
+        <v>2.2755</v>
       </c>
       <c r="G24" t="n">
         <v>1.4357</v>
@@ -2326,13 +2326,13 @@
         <v>2.2644</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1599</v>
+        <v>0.0132</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1793</v>
+        <v>-0.0156</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3391</v>
+        <v>0.0289</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3005</v>
+        <v>-1.5535</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4055</v>
+        <v>-3.9184</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1051</v>
+        <v>2.3649</v>
       </c>
       <c r="G25" t="n">
         <v>3.0935</v>
@@ -2404,13 +2404,13 @@
         <v>2.2644</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2105</v>
+        <v>0.9575</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1023</v>
+        <v>0.3848</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3128</v>
+        <v>0.5726</v>
       </c>
       <c r="V25" t="n">
         <v>0.6226</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>24.2662</v>
+        <v>25.5654</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9316</v>
+        <v>-1.931700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>26.1978</v>
+        <v>27.4971</v>
       </c>
       <c r="G26" t="n">
         <v>25.6179</v>
@@ -2482,13 +2482,13 @@
         <v>21.70050000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>2.460399999999999</v>
+        <v>3.7594</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1523000000000002</v>
+        <v>0.1522999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3081</v>
+        <v>3.6073</v>
       </c>
       <c r="V26" t="n">
         <v>0.9054</v>
